--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>98353</v>
+        <v>57933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R2" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,42 +786,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>57932</v>
+        <v>98354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R3" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>99082</v>
+        <v>107203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,26 +1015,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R5" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>107202</v>
+        <v>99083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R6" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>126003828</v>
       </c>
       <c r="B9" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>110411</v>
+        <v>110412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003839</v>
+        <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>98309</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720484</v>
+        <v>720610</v>
       </c>
       <c r="R13" t="n">
-        <v>6383205</v>
+        <v>6383025</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,6 +1966,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1974,11 +1979,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109144</v>
+        <v>98310</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>109145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,43 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,11 +2179,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2192,6 +2187,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>98243</v>
+        <v>98354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2478,24 +2478,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R18" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2556,57 +2551,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>109145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R19" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,48 +2653,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>109144</v>
+        <v>98244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R20" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>126003865</v>
       </c>
       <c r="B23" t="n">
-        <v>99082</v>
+        <v>99083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>126003827</v>
       </c>
       <c r="B24" t="n">
-        <v>110411</v>
+        <v>110412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>126003858</v>
       </c>
       <c r="B25" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>126003846</v>
       </c>
       <c r="B26" t="n">
-        <v>98249</v>
+        <v>98250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>126003867</v>
       </c>
       <c r="B27" t="n">
-        <v>99082</v>
+        <v>99083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98241</v>
+        <v>98242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98354</v>
+        <v>98250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98249</v>
+        <v>98355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,47 +4123,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126003826</v>
+        <v>126004224</v>
       </c>
       <c r="B33" t="n">
-        <v>105355</v>
+        <v>57648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4172,10 +4167,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720484</v>
+        <v>720485</v>
       </c>
       <c r="R33" t="n">
-        <v>6383152</v>
+        <v>6383176</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4210,6 +4205,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4218,11 +4218,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4239,42 +4234,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126004224</v>
+        <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>57648</v>
+        <v>105356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720485</v>
+        <v>720484</v>
       </c>
       <c r="R34" t="n">
-        <v>6383176</v>
+        <v>6383152</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,11 +4321,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4334,6 +4329,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003852</v>
+        <v>126003860</v>
       </c>
       <c r="B4" t="n">
-        <v>109145</v>
+        <v>99085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,17 +930,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720436</v>
+        <v>720469</v>
       </c>
       <c r="R4" t="n">
-        <v>6383278</v>
+        <v>6383250</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>107203</v>
+        <v>109147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,43 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R5" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B6" t="n">
-        <v>99083</v>
+        <v>107205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R6" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003825</v>
+        <v>126003828</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>109147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,21 +1380,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720484</v>
+        <v>720483</v>
       </c>
       <c r="R8" t="n">
-        <v>6383152</v>
+        <v>6383162</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,32 +1453,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003828</v>
+        <v>126003825</v>
       </c>
       <c r="B9" t="n">
-        <v>109145</v>
+        <v>98357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1491,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720483</v>
+        <v>720484</v>
       </c>
       <c r="R9" t="n">
-        <v>6383162</v>
+        <v>6383152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1572,7 +1572,7 @@
         <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>110412</v>
+        <v>110414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>109147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,43 +1895,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R13" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1966,11 +1957,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1965,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1998,7 +1989,7 @@
         <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126004223</v>
       </c>
       <c r="B15" t="n">
-        <v>109145</v>
+        <v>57648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,34 +2108,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720610</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383025</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,6 +2179,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2187,11 +2192,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,57 +2440,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B18" t="n">
-        <v>98354</v>
+        <v>109147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R18" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,48 +2542,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B19" t="n">
-        <v>109145</v>
+        <v>98246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R19" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,7 +2640,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2691,24 +2696,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R20" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,45 +2987,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003865</v>
+        <v>126003858</v>
       </c>
       <c r="B23" t="n">
-        <v>99083</v>
+        <v>98357</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222361</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720445</v>
+        <v>720469</v>
       </c>
       <c r="R23" t="n">
-        <v>6383250</v>
+        <v>6383238</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,11 +3074,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3076,7 +3085,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3094,27 +3103,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B24" t="n">
-        <v>110412</v>
+        <v>99085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3122,26 +3131,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R24" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3176,6 +3176,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3187,7 +3192,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3205,10 +3210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003858</v>
+        <v>126003827</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>110414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,26 +3221,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3243,21 +3248,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720469</v>
+        <v>720483</v>
       </c>
       <c r="R25" t="n">
-        <v>6383238</v>
+        <v>6383162</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3324,7 +3324,7 @@
         <v>126003846</v>
       </c>
       <c r="B26" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,37 +3432,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003867</v>
+        <v>126003868</v>
       </c>
       <c r="B27" t="n">
-        <v>99083</v>
+        <v>98244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222361</v>
+        <v>223572</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3519,11 +3519,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3553,37 +3548,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003868</v>
+        <v>126003867</v>
       </c>
       <c r="B28" t="n">
-        <v>98242</v>
+        <v>99085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223572</v>
+        <v>222361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3640,6 +3635,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98250</v>
+        <v>98357</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98252</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>98356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R2" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B3" t="n">
-        <v>98356</v>
+        <v>57933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R3" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003860</v>
+        <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>99085</v>
+        <v>109147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,26 +930,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720469</v>
+        <v>720436</v>
       </c>
       <c r="R4" t="n">
-        <v>6383250</v>
+        <v>6383278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>109147</v>
+        <v>107205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1015,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R5" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>107205</v>
+        <v>99085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R6" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003828</v>
+        <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>109147</v>
+        <v>98357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,16 +1380,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720483</v>
+        <v>720484</v>
       </c>
       <c r="R8" t="n">
-        <v>6383162</v>
+        <v>6383152</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003825</v>
+        <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>110414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,26 +1469,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1491,21 +1496,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720484</v>
+        <v>720467</v>
       </c>
       <c r="R9" t="n">
-        <v>6383152</v>
+        <v>6383211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>110414</v>
+        <v>109147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R10" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -3103,27 +3103,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B24" t="n">
-        <v>99085</v>
+        <v>110414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3131,17 +3131,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R24" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3176,11 +3185,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3192,7 +3196,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3210,27 +3214,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>110414</v>
+        <v>99085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3238,26 +3242,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R25" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3292,6 +3287,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>98356</v>
+        <v>57933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R2" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,42 +786,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>57933</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R3" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003852</v>
+        <v>126003860</v>
       </c>
       <c r="B4" t="n">
-        <v>109147</v>
+        <v>99089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,17 +930,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720436</v>
+        <v>720469</v>
       </c>
       <c r="R4" t="n">
-        <v>6383278</v>
+        <v>6383250</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>107205</v>
+        <v>109151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,43 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R5" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B6" t="n">
-        <v>99085</v>
+        <v>107209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R6" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B9" t="n">
-        <v>110414</v>
+        <v>109151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R9" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>109147</v>
+        <v>110418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R10" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003808</v>
+        <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>109147</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,34 +1895,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720598</v>
+        <v>720610</v>
       </c>
       <c r="R13" t="n">
-        <v>6383036</v>
+        <v>6383025</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,6 +1966,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1965,11 +1979,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1989,7 +1998,7 @@
         <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>109151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,43 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,11 +2179,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2192,6 +2187,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,48 +2440,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B18" t="n">
-        <v>109147</v>
+        <v>98250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R18" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2538,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2542,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B19" t="n">
-        <v>98246</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2580,24 +2594,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R19" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2649,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2658,57 +2667,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B20" t="n">
-        <v>98356</v>
+        <v>109151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R20" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003858</v>
+        <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>110418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2998,26 +2998,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3025,21 +3025,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720469</v>
+        <v>720483</v>
       </c>
       <c r="R23" t="n">
-        <v>6383238</v>
+        <v>6383162</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3103,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003827</v>
+        <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>110414</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,26 +3109,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3141,16 +3136,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720483</v>
+        <v>720469</v>
       </c>
       <c r="R24" t="n">
-        <v>6383162</v>
+        <v>6383238</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,7 +3217,7 @@
         <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>99085</v>
+        <v>99089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,37 +3321,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003846</v>
+        <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>98252</v>
+        <v>99089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3359,16 +3359,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720470</v>
+        <v>720436</v>
       </c>
       <c r="R26" t="n">
-        <v>6383213</v>
+        <v>6383278</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3403,6 +3408,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3414,7 +3424,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3432,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003868</v>
+        <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98244</v>
+        <v>98256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,26 +3453,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223572</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3470,21 +3480,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720436</v>
+        <v>720470</v>
       </c>
       <c r="R27" t="n">
-        <v>6383278</v>
+        <v>6383213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3548,37 +3553,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003867</v>
+        <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>99085</v>
+        <v>98248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222361</v>
+        <v>223572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3635,11 +3640,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>98256</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98252</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B4" t="n">
-        <v>99089</v>
+        <v>107210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R4" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,7 +1016,7 @@
         <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>107209</v>
+        <v>99090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R6" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>109151</v>
+        <v>110419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R9" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>110418</v>
+        <v>109152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R10" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>126003869</v>
       </c>
       <c r="B18" t="n">
-        <v>98250</v>
+        <v>98251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,57 +2556,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>109152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R19" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,48 +2658,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003833</v>
+        <v>126003817</v>
       </c>
       <c r="B20" t="n">
-        <v>109151</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720485</v>
+        <v>720531</v>
       </c>
       <c r="R20" t="n">
-        <v>6383182</v>
+        <v>6383058</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>110418</v>
+        <v>110419</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>99089</v>
+        <v>99090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>99089</v>
+        <v>99090</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98256</v>
+        <v>98257</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98256</v>
+        <v>98362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98257</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R2" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>57933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R3" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004223</v>
+        <v>126003839</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>98317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720610</v>
+        <v>720484</v>
       </c>
       <c r="R13" t="n">
-        <v>6383025</v>
+        <v>6383205</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,11 +1966,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1974,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,57 +1995,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>98317</v>
+        <v>109152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126004223</v>
       </c>
       <c r="B15" t="n">
-        <v>109152</v>
+        <v>57648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,34 +2108,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720610</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383025</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,6 +2179,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2187,11 +2192,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3321,37 +3321,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003867</v>
+        <v>126003846</v>
       </c>
       <c r="B26" t="n">
-        <v>99090</v>
+        <v>98257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3359,21 +3359,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720436</v>
+        <v>720470</v>
       </c>
       <c r="R26" t="n">
-        <v>6383278</v>
+        <v>6383213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3408,11 +3403,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3424,7 +3414,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3442,10 +3432,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003846</v>
+        <v>126003868</v>
       </c>
       <c r="B27" t="n">
-        <v>98257</v>
+        <v>98249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,26 +3443,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>223572</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3480,16 +3470,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720470</v>
+        <v>720436</v>
       </c>
       <c r="R27" t="n">
-        <v>6383213</v>
+        <v>6383278</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3553,37 +3548,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003868</v>
+        <v>126003867</v>
       </c>
       <c r="B28" t="n">
-        <v>98249</v>
+        <v>99090</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223572</v>
+        <v>222361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3640,6 +3635,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98362</v>
+        <v>98257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98257</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>57933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R2" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,42 +786,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>57933</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R3" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003839</v>
+        <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>98317</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720484</v>
+        <v>720610</v>
       </c>
       <c r="R13" t="n">
-        <v>6383205</v>
+        <v>6383025</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,6 +1966,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1974,11 +1979,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109152</v>
+        <v>98317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>109152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,43 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,11 +2179,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2192,6 +2187,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98257</v>
+        <v>98362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>98257</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4348,6 +4348,1952 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126192162</v>
+      </c>
+      <c r="B35" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720393</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6383111</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126192175</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720553</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6382997</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tallplantage, lite äldre.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126192170</v>
+      </c>
+      <c r="B37" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720460</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6383023</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126192290</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720624</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6383024</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126192172</v>
+      </c>
+      <c r="B39" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720507</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6383015</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Tallplantage, lite äldre.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126192289</v>
+      </c>
+      <c r="B40" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720624</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6383024</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126192167</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105923</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720443</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6383033</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126192283</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99014</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720675</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6383047</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126192281</v>
+      </c>
+      <c r="B43" t="n">
+        <v>105261</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720676</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6383061</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126192169</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720460</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6383023</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126192160</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720393</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6383111</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126192158</v>
+      </c>
+      <c r="B46" t="n">
+        <v>105923</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720383</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6383111</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126192282</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99014</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720676</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6383061</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126192165</v>
+      </c>
+      <c r="B48" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6383069</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126192287</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720648</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6383009</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126192174</v>
+      </c>
+      <c r="B50" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>720553</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6382997</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Tallplantage, lite äldre.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126192155</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720383</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6383111</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126192292</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Burs 1:3 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720624</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6383024</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>107210</v>
+        <v>109154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,43 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R4" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>109152</v>
+        <v>107212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1015,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R5" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>99090</v>
+        <v>99092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004223</v>
+        <v>126003839</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>98319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720610</v>
+        <v>720484</v>
       </c>
       <c r="R13" t="n">
-        <v>6383025</v>
+        <v>6383205</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,11 +1966,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1974,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,57 +1995,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>98317</v>
+        <v>109154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126004223</v>
       </c>
       <c r="B15" t="n">
-        <v>109152</v>
+        <v>57649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,34 +2108,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720610</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383025</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,6 +2179,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2187,11 +2192,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>98251</v>
+        <v>98363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2478,24 +2478,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R18" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2559,7 +2554,7 @@
         <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003817</v>
+        <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>98253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,21 +2664,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>223585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2696,19 +2691,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720531</v>
+        <v>720428</v>
       </c>
       <c r="R20" t="n">
-        <v>6383058</v>
+        <v>6383290</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>99090</v>
+        <v>99092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,37 +3321,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003846</v>
+        <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>98257</v>
+        <v>99092</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3359,16 +3359,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720470</v>
+        <v>720436</v>
       </c>
       <c r="R26" t="n">
-        <v>6383213</v>
+        <v>6383278</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3403,6 +3408,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3414,7 +3424,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3432,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003868</v>
+        <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98249</v>
+        <v>98259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,26 +3453,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223572</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3470,21 +3480,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720436</v>
+        <v>720470</v>
       </c>
       <c r="R27" t="n">
-        <v>6383278</v>
+        <v>6383213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3548,37 +3553,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003867</v>
+        <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>99090</v>
+        <v>98251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222361</v>
+        <v>223572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3635,11 +3640,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>126004224</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4350,45 +4350,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192162</v>
+        <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>109152</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720393</v>
+        <v>720553</v>
       </c>
       <c r="R35" t="n">
-        <v>6383111</v>
+        <v>6382997</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4423,11 +4432,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4439,7 +4443,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Tallplantage, lite äldre.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4457,54 +4461,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192175</v>
+        <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>98362</v>
+        <v>109154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720553</v>
+        <v>720393</v>
       </c>
       <c r="R36" t="n">
-        <v>6382997</v>
+        <v>6383111</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4539,6 +4534,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallplantage, lite äldre.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>126192170</v>
       </c>
       <c r="B37" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>126192290</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5207,37 +5207,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192281</v>
+        <v>126192169</v>
       </c>
       <c r="B43" t="n">
-        <v>105261</v>
+        <v>98319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5245,21 +5245,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720676</v>
+        <v>720460</v>
       </c>
       <c r="R43" t="n">
-        <v>6383061</v>
+        <v>6383023</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5294,11 +5289,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5310,7 +5300,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5328,37 +5318,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126192169</v>
+        <v>126192281</v>
       </c>
       <c r="B44" t="n">
-        <v>98317</v>
+        <v>105263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5366,16 +5356,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720460</v>
+        <v>720676</v>
       </c>
       <c r="R44" t="n">
-        <v>6383023</v>
+        <v>6383061</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5410,6 +5405,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126192158</v>
       </c>
       <c r="B46" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126192282</v>
       </c>
       <c r="B47" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B4" t="n">
-        <v>109154</v>
+        <v>107212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +913,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R4" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>107212</v>
+        <v>109154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,43 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R5" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003839</v>
+        <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>98319</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720484</v>
+        <v>720610</v>
       </c>
       <c r="R13" t="n">
-        <v>6383205</v>
+        <v>6383025</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,6 +1966,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1974,11 +1979,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109154</v>
+        <v>98319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>57649</v>
+        <v>109154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,43 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,11 +2179,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2192,6 +2187,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B4" t="n">
-        <v>107212</v>
+        <v>99094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R4" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,7 +1016,7 @@
         <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B6" t="n">
-        <v>99092</v>
+        <v>107214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R6" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B9" t="n">
-        <v>110421</v>
+        <v>109156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R9" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>109154</v>
+        <v>110423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R10" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,57 +1995,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>98319</v>
+        <v>109156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,48 +2097,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B15" t="n">
-        <v>109154</v>
+        <v>98321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>98253</v>
+        <v>98255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,27 +2987,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B23" t="n">
-        <v>110421</v>
+        <v>99094</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3015,26 +3015,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R23" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3069,6 +3060,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3076,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3101,7 +3097,7 @@
         <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,27 +3210,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B25" t="n">
-        <v>99092</v>
+        <v>110423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3242,17 +3238,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R25" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3287,11 +3292,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3321,37 +3321,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003867</v>
+        <v>126003846</v>
       </c>
       <c r="B26" t="n">
-        <v>99092</v>
+        <v>98261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3359,21 +3359,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720436</v>
+        <v>720470</v>
       </c>
       <c r="R26" t="n">
-        <v>6383278</v>
+        <v>6383213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3408,11 +3403,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3424,7 +3414,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3442,37 +3432,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003846</v>
+        <v>126003867</v>
       </c>
       <c r="B27" t="n">
-        <v>98259</v>
+        <v>99094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223591</v>
+        <v>222361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3480,16 +3470,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720470</v>
+        <v>720436</v>
       </c>
       <c r="R27" t="n">
-        <v>6383213</v>
+        <v>6383278</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3524,6 +3519,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>126192170</v>
       </c>
       <c r="B37" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>126192290</v>
       </c>
       <c r="B38" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>126192169</v>
       </c>
       <c r="B43" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>126192281</v>
       </c>
       <c r="B44" t="n">
-        <v>105263</v>
+        <v>105265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126192158</v>
       </c>
       <c r="B46" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126192282</v>
       </c>
       <c r="B47" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -1458,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>109156</v>
+        <v>110423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R9" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>110423</v>
+        <v>109156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R10" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004223</v>
+        <v>126003839</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>98321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720610</v>
+        <v>720484</v>
       </c>
       <c r="R13" t="n">
-        <v>6383025</v>
+        <v>6383205</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,11 +1966,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1974,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126004223</v>
       </c>
       <c r="B14" t="n">
-        <v>109156</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,34 +2006,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720610</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383025</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2068,6 +2077,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2076,11 +2090,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2097,57 +2106,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>98321</v>
+        <v>109156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003846</v>
+        <v>126003868</v>
       </c>
       <c r="B26" t="n">
-        <v>98261</v>
+        <v>98253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>223572</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3359,16 +3359,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720470</v>
+        <v>720436</v>
       </c>
       <c r="R26" t="n">
-        <v>6383213</v>
+        <v>6383278</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3414,7 +3419,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3432,37 +3437,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126003867</v>
+        <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>99094</v>
+        <v>98261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222361</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3470,21 +3475,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720436</v>
+        <v>720470</v>
       </c>
       <c r="R27" t="n">
-        <v>6383278</v>
+        <v>6383213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3519,11 +3519,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3553,37 +3548,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003868</v>
+        <v>126003867</v>
       </c>
       <c r="B28" t="n">
-        <v>98253</v>
+        <v>99094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223572</v>
+        <v>222361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3640,6 +3635,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4123,42 +4123,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126004224</v>
+        <v>126003826</v>
       </c>
       <c r="B33" t="n">
-        <v>57649</v>
+        <v>105367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4167,10 +4172,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720485</v>
+        <v>720484</v>
       </c>
       <c r="R33" t="n">
-        <v>6383176</v>
+        <v>6383152</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4205,11 +4210,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4218,6 +4218,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4234,47 +4239,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126003826</v>
+        <v>126004224</v>
       </c>
       <c r="B34" t="n">
-        <v>105367</v>
+        <v>57649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720484</v>
+        <v>720485</v>
       </c>
       <c r="R34" t="n">
-        <v>6383152</v>
+        <v>6383176</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4321,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,11 +4334,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B2" t="n">
-        <v>57934</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R2" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>57934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R3" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003860</v>
+        <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>99094</v>
+        <v>109160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,26 +930,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720469</v>
+        <v>720436</v>
       </c>
       <c r="R4" t="n">
-        <v>6383250</v>
+        <v>6383278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>109156</v>
+        <v>107218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1015,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R5" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>107214</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R6" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003825</v>
+        <v>126003828</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>109160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,21 +1380,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720484</v>
+        <v>720483</v>
       </c>
       <c r="R8" t="n">
-        <v>6383152</v>
+        <v>6383162</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003843</v>
+        <v>126003825</v>
       </c>
       <c r="B9" t="n">
-        <v>110423</v>
+        <v>98368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,26 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1496,16 +1491,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720467</v>
+        <v>720484</v>
       </c>
       <c r="R9" t="n">
-        <v>6383211</v>
+        <v>6383152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>109156</v>
+        <v>110427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R10" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003839</v>
+        <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>98321</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720484</v>
+        <v>720610</v>
       </c>
       <c r="R13" t="n">
-        <v>6383205</v>
+        <v>6383025</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,6 +1966,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i stubbe.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1974,11 +1979,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126004223</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>109160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,43 +2006,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720610</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383025</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,11 +2068,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i stubbe.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2090,6 +2076,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2106,48 +2097,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B15" t="n">
-        <v>109156</v>
+        <v>98323</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,57 +2440,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>109160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R18" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,48 +2542,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003833</v>
+        <v>126003817</v>
       </c>
       <c r="B19" t="n">
-        <v>109156</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720485</v>
+        <v>720531</v>
       </c>
       <c r="R19" t="n">
-        <v>6383182</v>
+        <v>6383058</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>98255</v>
+        <v>98257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,27 +2987,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>99094</v>
+        <v>110427</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3015,17 +3015,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R23" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,11 +3069,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3097,7 +3101,7 @@
         <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,27 +3214,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>110423</v>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3238,26 +3242,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R25" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3292,6 +3287,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3321,37 +3321,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126003868</v>
+        <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>98253</v>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223572</v>
+        <v>222361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3408,6 +3408,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3419,7 +3424,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3440,7 +3445,7 @@
         <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,37 +3553,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126003867</v>
+        <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>99094</v>
+        <v>98255</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222361</v>
+        <v>223572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3635,11 +3640,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,47 +4123,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126003826</v>
+        <v>126004224</v>
       </c>
       <c r="B33" t="n">
-        <v>105367</v>
+        <v>57649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4172,10 +4167,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720484</v>
+        <v>720485</v>
       </c>
       <c r="R33" t="n">
-        <v>6383152</v>
+        <v>6383176</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4210,6 +4205,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4218,11 +4218,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4239,42 +4234,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126004224</v>
+        <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>57649</v>
+        <v>105371</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720485</v>
+        <v>720484</v>
       </c>
       <c r="R34" t="n">
-        <v>6383176</v>
+        <v>6383152</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,11 +4321,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4334,6 +4329,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4353,7 +4353,7 @@
         <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,45 +4568,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192170</v>
+        <v>126192290</v>
       </c>
       <c r="B37" t="n">
-        <v>109156</v>
+        <v>98367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720460</v>
+        <v>720624</v>
       </c>
       <c r="R37" t="n">
-        <v>6383023</v>
+        <v>6383024</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4661,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4670,54 +4679,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126192290</v>
+        <v>126192170</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>109160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720624</v>
+        <v>720460</v>
       </c>
       <c r="R38" t="n">
-        <v>6383024</v>
+        <v>6383023</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99018</v>
+        <v>99020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>126192169</v>
       </c>
       <c r="B43" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>126192281</v>
       </c>
       <c r="B44" t="n">
-        <v>105265</v>
+        <v>105269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192158</v>
+        <v>126192282</v>
       </c>
       <c r="B46" t="n">
-        <v>105927</v>
+        <v>99020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720383</v>
+        <v>720676</v>
       </c>
       <c r="R46" t="n">
-        <v>6383111</v>
+        <v>6383061</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5652,32 +5652,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192282</v>
+        <v>126192158</v>
       </c>
       <c r="B47" t="n">
-        <v>99018</v>
+        <v>105931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222322</v>
+        <v>220785</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720676</v>
+        <v>720383</v>
       </c>
       <c r="R47" t="n">
-        <v>6383061</v>
+        <v>6383111</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98263</v>
+        <v>98368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4350,54 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192175</v>
+        <v>126192162</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>109160</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720553</v>
+        <v>720393</v>
       </c>
       <c r="R35" t="n">
-        <v>6382997</v>
+        <v>6383111</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4432,6 +4423,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4443,7 +4439,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Tallplantage, lite äldre.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4461,45 +4457,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192162</v>
+        <v>126192175</v>
       </c>
       <c r="B36" t="n">
-        <v>109160</v>
+        <v>98368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720393</v>
+        <v>720553</v>
       </c>
       <c r="R36" t="n">
-        <v>6383111</v>
+        <v>6382997</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4534,11 +4539,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Tallplantage, lite äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003811</v>
+        <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>57938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720584</v>
+        <v>720445</v>
       </c>
       <c r="R2" t="n">
-        <v>6383032</v>
+        <v>6383241</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,42 +786,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126004108</v>
+        <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>57934</v>
+        <v>98371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720445</v>
+        <v>720584</v>
       </c>
       <c r="R3" t="n">
-        <v>6383241</v>
+        <v>6383032</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B4" t="n">
-        <v>109160</v>
+        <v>107231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +913,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R4" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>107218</v>
+        <v>109173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,43 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R5" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>99096</v>
+        <v>99100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003828</v>
+        <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>109160</v>
+        <v>98372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,16 +1380,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720483</v>
+        <v>720484</v>
       </c>
       <c r="R8" t="n">
-        <v>6383162</v>
+        <v>6383152</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003825</v>
+        <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>110440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,26 +1469,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1491,21 +1496,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720484</v>
+        <v>720467</v>
       </c>
       <c r="R9" t="n">
-        <v>6383152</v>
+        <v>6383211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>110427</v>
+        <v>109173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R10" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>126003845</v>
       </c>
       <c r="B11" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126003859</v>
       </c>
       <c r="B12" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109160</v>
+        <v>98327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,57 +2106,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>98323</v>
+        <v>109173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>126003833</v>
       </c>
       <c r="B18" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003817</v>
+        <v>126003869</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>98261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>223585</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2580,19 +2580,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720531</v>
+        <v>720428</v>
       </c>
       <c r="R19" t="n">
-        <v>6383058</v>
+        <v>6383290</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,7 +2640,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B20" t="n">
-        <v>98257</v>
+        <v>98371</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2691,24 +2696,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R20" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003827</v>
+        <v>126003858</v>
       </c>
       <c r="B23" t="n">
-        <v>110427</v>
+        <v>98372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2998,26 +2998,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3025,16 +3025,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720483</v>
+        <v>720469</v>
       </c>
       <c r="R23" t="n">
-        <v>6383162</v>
+        <v>6383238</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3098,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003858</v>
+        <v>126003827</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>110440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,26 +3114,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3136,21 +3141,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720469</v>
+        <v>720483</v>
       </c>
       <c r="R24" t="n">
-        <v>6383238</v>
+        <v>6383162</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,7 +3217,7 @@
         <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>99096</v>
+        <v>99100</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>99096</v>
+        <v>99100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98255</v>
+        <v>98259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98263</v>
+        <v>98372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>126004224</v>
       </c>
       <c r="B33" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>126192162</v>
       </c>
       <c r="B35" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>126192175</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,54 +4568,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192290</v>
+        <v>126192170</v>
       </c>
       <c r="B37" t="n">
-        <v>98367</v>
+        <v>109173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720624</v>
+        <v>720460</v>
       </c>
       <c r="R37" t="n">
-        <v>6383024</v>
+        <v>6383023</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,7 +4652,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4679,45 +4670,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126192170</v>
+        <v>126192290</v>
       </c>
       <c r="B38" t="n">
-        <v>109160</v>
+        <v>98371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720460</v>
+        <v>720624</v>
       </c>
       <c r="R38" t="n">
-        <v>6383023</v>
+        <v>6383024</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5207,37 +5207,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192169</v>
+        <v>126192281</v>
       </c>
       <c r="B43" t="n">
-        <v>98323</v>
+        <v>105282</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5245,16 +5245,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720460</v>
+        <v>720676</v>
       </c>
       <c r="R43" t="n">
-        <v>6383023</v>
+        <v>6383061</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5289,6 +5294,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5300,7 +5310,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5318,37 +5328,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126192281</v>
+        <v>126192169</v>
       </c>
       <c r="B44" t="n">
-        <v>105269</v>
+        <v>98327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5356,21 +5366,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720676</v>
+        <v>720460</v>
       </c>
       <c r="R44" t="n">
-        <v>6383061</v>
+        <v>6383023</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5405,11 +5410,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192282</v>
+        <v>126192158</v>
       </c>
       <c r="B46" t="n">
-        <v>99020</v>
+        <v>105944</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222322</v>
+        <v>220785</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720676</v>
+        <v>720383</v>
       </c>
       <c r="R46" t="n">
-        <v>6383061</v>
+        <v>6383111</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5652,32 +5652,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192158</v>
+        <v>126192282</v>
       </c>
       <c r="B47" t="n">
-        <v>105931</v>
+        <v>99024</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720383</v>
+        <v>720676</v>
       </c>
       <c r="R47" t="n">
-        <v>6383111</v>
+        <v>6383061</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -2987,59 +2987,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003858</v>
+        <v>126003865</v>
       </c>
       <c r="B23" t="n">
-        <v>98372</v>
+        <v>99100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>222361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720469</v>
+        <v>720445</v>
       </c>
       <c r="R23" t="n">
-        <v>6383238</v>
+        <v>6383250</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3074,6 +3060,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3085,7 +3076,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3103,10 +3094,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003827</v>
+        <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>110440</v>
+        <v>98372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,26 +3105,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3141,16 +3132,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720483</v>
+        <v>720469</v>
       </c>
       <c r="R24" t="n">
-        <v>6383162</v>
+        <v>6383238</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3214,27 +3210,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B25" t="n">
-        <v>99100</v>
+        <v>110440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3242,17 +3238,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R25" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3287,11 +3292,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126004032</v>
+        <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>107231</v>
+        <v>109176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,43 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720571</v>
+        <v>720436</v>
       </c>
       <c r="R4" t="n">
-        <v>6383044</v>
+        <v>6383278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>109173</v>
+        <v>107234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1015,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R5" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>99100</v>
+        <v>99103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003843</v>
+        <v>126003828</v>
       </c>
       <c r="B9" t="n">
-        <v>110440</v>
+        <v>109176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720467</v>
+        <v>720483</v>
       </c>
       <c r="R9" t="n">
-        <v>6383211</v>
+        <v>6383162</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,27 +1569,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B10" t="n">
-        <v>109173</v>
+        <v>110443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R10" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126003845</v>
+        <v>126003859</v>
       </c>
       <c r="B11" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720470</v>
+        <v>720469</v>
       </c>
       <c r="R11" t="n">
-        <v>6383213</v>
+        <v>6383250</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003859</v>
+        <v>126003845</v>
       </c>
       <c r="B12" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720469</v>
+        <v>720470</v>
       </c>
       <c r="R12" t="n">
-        <v>6383250</v>
+        <v>6383213</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1995,57 +1995,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>98327</v>
+        <v>109176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,48 +2097,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B15" t="n">
-        <v>109173</v>
+        <v>98330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,48 +2440,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B18" t="n">
-        <v>109173</v>
+        <v>98264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R18" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2538,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2542,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B19" t="n">
-        <v>98261</v>
+        <v>98374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2580,24 +2594,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R19" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2649,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2658,57 +2667,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B20" t="n">
-        <v>98371</v>
+        <v>109176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R20" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,27 +2987,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>99100</v>
+        <v>110443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3015,17 +3015,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R23" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,11 +3069,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3097,7 +3101,7 @@
         <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,27 +3214,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>110440</v>
+        <v>99103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3238,26 +3242,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R25" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3292,6 +3287,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3324,7 +3324,7 @@
         <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>99100</v>
+        <v>99103</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4350,45 +4350,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192162</v>
+        <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>109173</v>
+        <v>98375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720393</v>
+        <v>720553</v>
       </c>
       <c r="R35" t="n">
-        <v>6383111</v>
+        <v>6382997</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4423,11 +4432,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4439,7 +4443,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Tallplantage, lite äldre.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4457,54 +4461,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192175</v>
+        <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>98372</v>
+        <v>109176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720553</v>
+        <v>720393</v>
       </c>
       <c r="R36" t="n">
-        <v>6382997</v>
+        <v>6383111</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4539,6 +4534,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallplantage, lite äldre.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>126192170</v>
       </c>
       <c r="B37" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>126192290</v>
       </c>
       <c r="B38" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5207,37 +5207,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126192281</v>
+        <v>126192169</v>
       </c>
       <c r="B43" t="n">
-        <v>105282</v>
+        <v>98330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5245,21 +5245,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720676</v>
+        <v>720460</v>
       </c>
       <c r="R43" t="n">
-        <v>6383061</v>
+        <v>6383023</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5294,11 +5289,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5310,7 +5300,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5328,37 +5318,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126192169</v>
+        <v>126192281</v>
       </c>
       <c r="B44" t="n">
-        <v>98327</v>
+        <v>105285</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5366,16 +5356,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720460</v>
+        <v>720676</v>
       </c>
       <c r="R44" t="n">
-        <v>6383023</v>
+        <v>6383061</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5410,6 +5405,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126192158</v>
       </c>
       <c r="B46" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126192282</v>
       </c>
       <c r="B47" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109176</v>
+        <v>98330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,57 +2106,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>98264</v>
+        <v>98374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2478,24 +2478,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R18" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2556,57 +2551,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>98374</v>
+        <v>109176</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R19" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,48 +2653,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>109176</v>
+        <v>98264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R20" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003825</v>
+        <v>126003828</v>
       </c>
       <c r="B8" t="n">
-        <v>98375</v>
+        <v>109176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,21 +1380,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720484</v>
+        <v>720483</v>
       </c>
       <c r="R8" t="n">
-        <v>6383152</v>
+        <v>6383162</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,32 +1453,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003828</v>
+        <v>126003825</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>98375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1491,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720483</v>
+        <v>720484</v>
       </c>
       <c r="R9" t="n">
-        <v>6383162</v>
+        <v>6383152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126003859</v>
+        <v>126003845</v>
       </c>
       <c r="B11" t="n">
         <v>109176</v>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720469</v>
+        <v>720470</v>
       </c>
       <c r="R11" t="n">
-        <v>6383250</v>
+        <v>6383213</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003845</v>
+        <v>126003859</v>
       </c>
       <c r="B12" t="n">
         <v>109176</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720470</v>
+        <v>720469</v>
       </c>
       <c r="R12" t="n">
-        <v>6383213</v>
+        <v>6383250</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1995,57 +1995,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B14" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,48 +2097,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B15" t="n">
-        <v>109176</v>
+        <v>98330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R15" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126003820</v>
+        <v>126003823</v>
       </c>
       <c r="B16" t="n">
-        <v>98374</v>
+        <v>98375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2219,26 +2219,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720521</v>
+        <v>720480</v>
       </c>
       <c r="R16" t="n">
-        <v>6383087</v>
+        <v>6383135</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126003823</v>
+        <v>126003820</v>
       </c>
       <c r="B17" t="n">
-        <v>98375</v>
+        <v>98374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,26 +2335,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720480</v>
+        <v>720521</v>
       </c>
       <c r="R17" t="n">
-        <v>6383135</v>
+        <v>6383087</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2987,27 +2987,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003827</v>
+        <v>126003865</v>
       </c>
       <c r="B23" t="n">
-        <v>110443</v>
+        <v>99103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>222361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3015,26 +3015,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R23" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3069,6 +3060,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3076,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3098,10 +3094,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003858</v>
+        <v>126003827</v>
       </c>
       <c r="B24" t="n">
-        <v>98375</v>
+        <v>110443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,26 +3105,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3136,21 +3132,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720469</v>
+        <v>720483</v>
       </c>
       <c r="R24" t="n">
-        <v>6383238</v>
+        <v>6383162</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3214,45 +3205,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003865</v>
+        <v>126003858</v>
       </c>
       <c r="B25" t="n">
-        <v>99103</v>
+        <v>98375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222361</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720445</v>
+        <v>720469</v>
       </c>
       <c r="R25" t="n">
-        <v>6383250</v>
+        <v>6383238</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3287,11 +3292,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98375</v>
+        <v>98270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98270</v>
+        <v>98375</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -1995,48 +1995,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003808</v>
+        <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>109176</v>
+        <v>98330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720598</v>
+        <v>720484</v>
       </c>
       <c r="R14" t="n">
-        <v>6383036</v>
+        <v>6383205</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,57 +2106,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003839</v>
+        <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720484</v>
+        <v>720598</v>
       </c>
       <c r="R15" t="n">
-        <v>6383205</v>
+        <v>6383036</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003817</v>
+        <v>126003869</v>
       </c>
       <c r="B18" t="n">
-        <v>98374</v>
+        <v>98264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>223585</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2478,19 +2478,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720531</v>
+        <v>720428</v>
       </c>
       <c r="R18" t="n">
-        <v>6383058</v>
+        <v>6383290</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2551,48 +2556,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003833</v>
+        <v>126003817</v>
       </c>
       <c r="B19" t="n">
-        <v>109176</v>
+        <v>98374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720485</v>
+        <v>720531</v>
       </c>
       <c r="R19" t="n">
-        <v>6383182</v>
+        <v>6383058</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,62 +2667,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003869</v>
+        <v>126003833</v>
       </c>
       <c r="B20" t="n">
-        <v>98264</v>
+        <v>109176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223585</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720428</v>
+        <v>720485</v>
       </c>
       <c r="R20" t="n">
-        <v>6383290</v>
+        <v>6383182</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98270</v>
+        <v>98375</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98375</v>
+        <v>98270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126004108</v>
       </c>
       <c r="B2" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126003811</v>
       </c>
       <c r="B3" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>126003852</v>
       </c>
       <c r="B4" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126004032</v>
       </c>
       <c r="B5" t="n">
-        <v>107234</v>
+        <v>107243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>99103</v>
+        <v>99112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>126003805</v>
       </c>
       <c r="B7" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,27 +1342,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B8" t="n">
-        <v>109176</v>
+        <v>110452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R8" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,32 +1453,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003825</v>
+        <v>126003828</v>
       </c>
       <c r="B9" t="n">
-        <v>98375</v>
+        <v>109185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1491,21 +1491,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720484</v>
+        <v>720483</v>
       </c>
       <c r="R9" t="n">
-        <v>6383152</v>
+        <v>6383162</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003843</v>
+        <v>126003825</v>
       </c>
       <c r="B10" t="n">
-        <v>110443</v>
+        <v>98384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,26 +1575,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1607,16 +1602,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720467</v>
+        <v>720484</v>
       </c>
       <c r="R10" t="n">
-        <v>6383211</v>
+        <v>6383152</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126003845</v>
+        <v>126003859</v>
       </c>
       <c r="B11" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720470</v>
+        <v>720469</v>
       </c>
       <c r="R11" t="n">
-        <v>6383213</v>
+        <v>6383250</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003859</v>
+        <v>126003845</v>
       </c>
       <c r="B12" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720469</v>
+        <v>720470</v>
       </c>
       <c r="R12" t="n">
-        <v>6383250</v>
+        <v>6383213</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1887,7 +1887,7 @@
         <v>126004223</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>126003839</v>
       </c>
       <c r="B14" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>126003808</v>
       </c>
       <c r="B15" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126003823</v>
+        <v>126003820</v>
       </c>
       <c r="B16" t="n">
-        <v>98375</v>
+        <v>98383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2219,26 +2219,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720480</v>
+        <v>720521</v>
       </c>
       <c r="R16" t="n">
-        <v>6383135</v>
+        <v>6383087</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126003820</v>
+        <v>126003823</v>
       </c>
       <c r="B17" t="n">
-        <v>98374</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,26 +2335,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720521</v>
+        <v>720480</v>
       </c>
       <c r="R17" t="n">
-        <v>6383087</v>
+        <v>6383135</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>98264</v>
+        <v>98383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2478,24 +2478,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R18" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003817</v>
+        <v>126003869</v>
       </c>
       <c r="B19" t="n">
-        <v>98374</v>
+        <v>98273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>223585</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2594,19 +2589,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720531</v>
+        <v>720428</v>
       </c>
       <c r="R19" t="n">
-        <v>6383058</v>
+        <v>6383290</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
         <v>126003833</v>
       </c>
       <c r="B20" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126003812</v>
       </c>
       <c r="B21" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126003856</v>
       </c>
       <c r="B22" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>126003865</v>
       </c>
       <c r="B23" t="n">
-        <v>99103</v>
+        <v>99112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>126003827</v>
       </c>
       <c r="B24" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>126003858</v>
       </c>
       <c r="B25" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>126003867</v>
       </c>
       <c r="B26" t="n">
-        <v>99103</v>
+        <v>99112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>126003846</v>
       </c>
       <c r="B27" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>126003868</v>
       </c>
       <c r="B28" t="n">
-        <v>98262</v>
+        <v>98271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>126003855</v>
       </c>
       <c r="B29" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B30" t="n">
-        <v>98375</v>
+        <v>98279</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,21 +3823,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R30" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3901,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B31" t="n">
-        <v>98270</v>
+        <v>98384</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,26 +3907,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3939,16 +3934,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R31" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>126003830</v>
       </c>
       <c r="B32" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>126004224</v>
       </c>
       <c r="B33" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126003826</v>
       </c>
       <c r="B34" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,45 +4568,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126192170</v>
+        <v>126192290</v>
       </c>
       <c r="B37" t="n">
-        <v>109176</v>
+        <v>98383</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720460</v>
+        <v>720624</v>
       </c>
       <c r="R37" t="n">
-        <v>6383023</v>
+        <v>6383024</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4652,7 +4661,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4670,54 +4679,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126192290</v>
+        <v>126192170</v>
       </c>
       <c r="B38" t="n">
-        <v>98374</v>
+        <v>109185</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720624</v>
+        <v>720460</v>
       </c>
       <c r="R38" t="n">
-        <v>6383024</v>
+        <v>6383023</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
         <v>126192172</v>
       </c>
       <c r="B39" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>126192289</v>
       </c>
       <c r="B40" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>126192167</v>
       </c>
       <c r="B41" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>126192283</v>
       </c>
       <c r="B42" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>126192169</v>
       </c>
       <c r="B43" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>126192281</v>
       </c>
       <c r="B44" t="n">
-        <v>105285</v>
+        <v>105294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>126192160</v>
       </c>
       <c r="B45" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126192158</v>
       </c>
       <c r="B46" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>126192282</v>
       </c>
       <c r="B47" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>126192165</v>
       </c>
       <c r="B48" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>126192287</v>
       </c>
       <c r="B49" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>126192174</v>
       </c>
       <c r="B50" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>126192155</v>
       </c>
       <c r="B51" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>126192292</v>
       </c>
       <c r="B52" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -4123,42 +4123,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126004224</v>
+        <v>126003826</v>
       </c>
       <c r="B33" t="n">
-        <v>57654</v>
+        <v>105396</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4167,10 +4172,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720485</v>
+        <v>720484</v>
       </c>
       <c r="R33" t="n">
-        <v>6383176</v>
+        <v>6383152</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4205,11 +4210,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4218,6 +4218,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4234,47 +4239,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126003826</v>
+        <v>126004224</v>
       </c>
       <c r="B34" t="n">
-        <v>105396</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720484</v>
+        <v>720485</v>
       </c>
       <c r="R34" t="n">
-        <v>6383152</v>
+        <v>6383176</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4321,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,11 +4334,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B5" t="n">
-        <v>107243</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,26 +1015,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R5" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003860</v>
+        <v>126004032</v>
       </c>
       <c r="B6" t="n">
-        <v>99112</v>
+        <v>107243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720469</v>
+        <v>720571</v>
       </c>
       <c r="R6" t="n">
-        <v>6383250</v>
+        <v>6383044</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003843</v>
+        <v>126003825</v>
       </c>
       <c r="B8" t="n">
-        <v>110452</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,26 +1353,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1380,16 +1380,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720467</v>
+        <v>720484</v>
       </c>
       <c r="R8" t="n">
-        <v>6383211</v>
+        <v>6383152</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003828</v>
+        <v>126003843</v>
       </c>
       <c r="B9" t="n">
-        <v>109185</v>
+        <v>110452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1483,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1497,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720483</v>
+        <v>720467</v>
       </c>
       <c r="R9" t="n">
-        <v>6383162</v>
+        <v>6383211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,32 +1569,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126003825</v>
+        <v>126003828</v>
       </c>
       <c r="B10" t="n">
-        <v>98384</v>
+        <v>109185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1602,21 +1607,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720484</v>
+        <v>720483</v>
       </c>
       <c r="R10" t="n">
-        <v>6383152</v>
+        <v>6383162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126003859</v>
+        <v>126003845</v>
       </c>
       <c r="B11" t="n">
         <v>109185</v>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720469</v>
+        <v>720470</v>
       </c>
       <c r="R11" t="n">
-        <v>6383250</v>
+        <v>6383213</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003845</v>
+        <v>126003859</v>
       </c>
       <c r="B12" t="n">
         <v>109185</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720470</v>
+        <v>720469</v>
       </c>
       <c r="R12" t="n">
-        <v>6383213</v>
+        <v>6383250</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2440,57 +2440,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B18" t="n">
-        <v>98383</v>
+        <v>109185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R18" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2667,48 +2658,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003833</v>
+        <v>126003817</v>
       </c>
       <c r="B20" t="n">
-        <v>109185</v>
+        <v>98383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720485</v>
+        <v>720531</v>
       </c>
       <c r="R20" t="n">
-        <v>6383182</v>
+        <v>6383058</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2987,27 +2987,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126003865</v>
+        <v>126003827</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>110452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222361</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3015,17 +3015,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R23" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,11 +3069,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3094,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126003827</v>
+        <v>126003858</v>
       </c>
       <c r="B24" t="n">
-        <v>110452</v>
+        <v>98384</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3105,26 +3109,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3132,16 +3136,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720483</v>
+        <v>720469</v>
       </c>
       <c r="R24" t="n">
-        <v>6383162</v>
+        <v>6383238</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3205,59 +3214,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126003858</v>
+        <v>126003865</v>
       </c>
       <c r="B25" t="n">
-        <v>98384</v>
+        <v>99112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>222361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720469</v>
+        <v>720445</v>
       </c>
       <c r="R25" t="n">
-        <v>6383238</v>
+        <v>6383250</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3292,6 +3287,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126003829</v>
+        <v>126003864</v>
       </c>
       <c r="B30" t="n">
-        <v>98279</v>
+        <v>98384</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,26 +3796,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3823,16 +3823,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720483</v>
+        <v>720445</v>
       </c>
       <c r="R30" t="n">
-        <v>6383162</v>
+        <v>6383250</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3896,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126003864</v>
+        <v>126003829</v>
       </c>
       <c r="B31" t="n">
-        <v>98384</v>
+        <v>98279</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,26 +3912,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,21 +3939,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720445</v>
+        <v>720483</v>
       </c>
       <c r="R31" t="n">
-        <v>6383250</v>
+        <v>6383162</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr, kant med blåtåteltuvor..</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4350,54 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192175</v>
+        <v>126192162</v>
       </c>
       <c r="B35" t="n">
-        <v>98384</v>
+        <v>109185</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720553</v>
+        <v>720393</v>
       </c>
       <c r="R35" t="n">
-        <v>6382997</v>
+        <v>6383111</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4432,6 +4423,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4443,7 +4439,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Tallplantage, lite äldre.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4461,45 +4457,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192162</v>
+        <v>126192175</v>
       </c>
       <c r="B36" t="n">
-        <v>109185</v>
+        <v>98384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720393</v>
+        <v>720553</v>
       </c>
       <c r="R36" t="n">
-        <v>6383111</v>
+        <v>6382997</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4534,11 +4539,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Tallplantage, lite äldre.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126192158</v>
+        <v>126192282</v>
       </c>
       <c r="B46" t="n">
-        <v>105956</v>
+        <v>99036</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720383</v>
+        <v>720676</v>
       </c>
       <c r="R46" t="n">
-        <v>6383111</v>
+        <v>6383061</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5652,32 +5652,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126192282</v>
+        <v>126192158</v>
       </c>
       <c r="B47" t="n">
-        <v>99036</v>
+        <v>105956</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222322</v>
+        <v>220785</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720676</v>
+        <v>720383</v>
       </c>
       <c r="R47" t="n">
-        <v>6383061</v>
+        <v>6383111</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Gränsgata, körspår.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -2440,48 +2440,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003833</v>
+        <v>126003817</v>
       </c>
       <c r="B18" t="n">
-        <v>109185</v>
+        <v>98383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720485</v>
+        <v>720531</v>
       </c>
       <c r="R18" t="n">
-        <v>6383182</v>
+        <v>6383058</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,62 +2551,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003869</v>
+        <v>126003833</v>
       </c>
       <c r="B19" t="n">
-        <v>98273</v>
+        <v>109185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223585</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720428</v>
+        <v>720485</v>
       </c>
       <c r="R19" t="n">
-        <v>6383290</v>
+        <v>6383182</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2635,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003817</v>
+        <v>126003869</v>
       </c>
       <c r="B20" t="n">
-        <v>98383</v>
+        <v>98273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,21 +2664,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>223585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2696,19 +2691,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720531</v>
+        <v>720428</v>
       </c>
       <c r="R20" t="n">
-        <v>6383058</v>
+        <v>6383290</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126003852</v>
+        <v>126004032</v>
       </c>
       <c r="B4" t="n">
-        <v>109185</v>
+        <v>107243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +913,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720436</v>
+        <v>720571</v>
       </c>
       <c r="R4" t="n">
-        <v>6383278</v>
+        <v>6383044</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003860</v>
+        <v>126003852</v>
       </c>
       <c r="B5" t="n">
-        <v>99112</v>
+        <v>109185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,16 +1024,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,26 +1041,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720469</v>
+        <v>720436</v>
       </c>
       <c r="R5" t="n">
-        <v>6383250</v>
+        <v>6383278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126004032</v>
+        <v>126003860</v>
       </c>
       <c r="B6" t="n">
-        <v>107243</v>
+        <v>99112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,26 +1126,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>222361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720571</v>
+        <v>720469</v>
       </c>
       <c r="R6" t="n">
-        <v>6383044</v>
+        <v>6383250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -2440,57 +2440,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126003817</v>
+        <v>126003833</v>
       </c>
       <c r="B18" t="n">
-        <v>98383</v>
+        <v>109185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720531</v>
+        <v>720485</v>
       </c>
       <c r="R18" t="n">
-        <v>6383058</v>
+        <v>6383182</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,48 +2542,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003833</v>
+        <v>126003869</v>
       </c>
       <c r="B19" t="n">
-        <v>109185</v>
+        <v>98273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>223585</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Wüstnei ex Boll) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720485</v>
+        <v>720428</v>
       </c>
       <c r="R19" t="n">
-        <v>6383182</v>
+        <v>6383290</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,7 +2640,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003869</v>
+        <v>126003817</v>
       </c>
       <c r="B20" t="n">
-        <v>98273</v>
+        <v>98383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223585</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2691,24 +2696,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720428</v>
+        <v>720531</v>
       </c>
       <c r="R20" t="n">
-        <v>6383290</v>
+        <v>6383058</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -4350,45 +4350,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126192162</v>
+        <v>126192175</v>
       </c>
       <c r="B35" t="n">
-        <v>109185</v>
+        <v>98384</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720393</v>
+        <v>720553</v>
       </c>
       <c r="R35" t="n">
-        <v>6383111</v>
+        <v>6382997</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4423,11 +4432,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4439,7 +4443,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
+          <t>Tallplantage, lite äldre.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4457,54 +4461,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126192175</v>
+        <v>126192162</v>
       </c>
       <c r="B36" t="n">
-        <v>98384</v>
+        <v>109185</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720553</v>
+        <v>720393</v>
       </c>
       <c r="R36" t="n">
-        <v>6382997</v>
+        <v>6383111</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4539,6 +4534,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallplantage, lite äldre.</t>
+          <t>Kalkbarrskog med kontinuitet, nyröjt inför avvekning.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6294,6 +6294,103 @@
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128811523</v>
+      </c>
+      <c r="B53" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gothem Suderbys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720643</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6383078</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6913-2025 artfynd.xlsx
+++ b/artfynd/A 6913-2025 artfynd.xlsx
@@ -6299,7 +6299,7 @@
         <v>128811523</v>
       </c>
       <c r="B53" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
